--- a/files/Performance_2yr_2024_2025.xlsx
+++ b/files/Performance_2yr_2024_2025.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variance" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+  </numFmts>
   <fonts count="5">
     <font>
       <name val="Calibri"/>
@@ -26,26 +28,30 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="14"/>
+      <sz val="16"/>
     </font>
     <font>
-      <i val="1"/>
-      <color rgb="006B7280"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
-    <font>
+      <name val="Calibri"/>
       <i val="1"/>
       <color rgb="006B7280"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00222222"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -55,10 +61,17 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F2D55"/>
+        <bgColor rgb="001F2D55"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4F6FB"/>
+        <bgColor rgb="00F4F6FB"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -66,22 +79,53 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D0D7E2"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D0D7E2"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D7E2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D7E2"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -447,17 +491,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Performance 2yr 2024 2025</t>
@@ -467,11 +514,11 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Performance_2yr_2024_2025.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
+          <t>Source file: Performance_2yr_2024_2025.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Metric</t>
@@ -479,99 +526,1676 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>Division</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>Period</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>FY2026 Plan</t>
+          <t>Plan</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Variance</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Var %</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>RAG</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Revenue (RM m)</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1850</v>
-      </c>
-      <c r="C5" t="n">
-        <v>2020</v>
-      </c>
-      <c r="D5" t="n">
-        <v>2210</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>CAGR ~9%</t>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Revenue (MYR M)</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>FY2026 Q1</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>740.5</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>767</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Amber</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>EBITDA (RM m)</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>412</v>
-      </c>
-      <c r="C6" t="n">
-        <v>455</v>
-      </c>
-      <c r="D6" t="n">
-        <v>510</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Margin lift</t>
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>EBITDA (MYR M)</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>FY2026 Q1</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>128.2</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>137.3</v>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="G6" s="9" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>Red</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Net Margin (%)</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="C7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="D7" t="n">
-        <v>13</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Above peer median</t>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Free cash flow (MYR M)</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>FY2026 Q1</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>88.2</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Net working capital days</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>FY2026 Q1</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>-0.024</v>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>Green</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Note: placeholder demo data — not real Zava figures.</t>
+          <t>Operating margin %</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>FY2026 Q1</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Cost-to-income %</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>FY2026 Q1</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G10" s="9" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Revenue (MYR M)</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>FY2026 Q1</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>748.4</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>720.5</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-27.9</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.037</v>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>Amber</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>EBITDA (MYR M)</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>FY2026 Q1</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>141</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>132.1</v>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>-8.9</v>
+      </c>
+      <c r="G12" s="9" t="n">
+        <v>-0.063</v>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>Amber</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Free cash flow (MYR M)</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>FY2026 Q1</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>Amber</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Net working capital days</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>FY2026 Q1</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>51</v>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="G14" s="9" t="n">
+        <v>-0.029</v>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Operating margin %</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>FY2026 Q1</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Amber</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Cost-to-income %</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>FY2026 Q1</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>44.7</v>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" s="9" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>Amber</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Revenue (MYR M)</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Healthcare Services</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>FY2026 Q1</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>728.8</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>733.6</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>EBITDA (MYR M)</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Healthcare Services</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>FY2026 Q1</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="n">
+        <v>141.9</v>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>149.1</v>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="G18" s="9" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>Amber</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Free cash flow (MYR M)</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Healthcare Services</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>FY2026 Q1</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>91.5</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>Amber</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Net working capital days</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Healthcare Services</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>FY2026 Q1</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="G20" s="9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Operating margin %</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Healthcare Services</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>FY2026 Q1</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>Amber</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Cost-to-income %</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Healthcare Services</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>FY2026 Q1</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="F22" s="8" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="G22" s="9" t="n">
+        <v>-0.042</v>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>Amber</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Revenue (MYR M)</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Industrial Mfg</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>FY2026 Q1</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>755.7</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>779</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>Amber</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>EBITDA (MYR M)</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Industrial Mfg</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>FY2026 Q1</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="n">
+        <v>137.3</v>
+      </c>
+      <c r="E24" s="8" t="n">
+        <v>134</v>
+      </c>
+      <c r="F24" s="8" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="G24" s="9" t="n">
+        <v>-0.024</v>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Free cash flow (MYR M)</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Industrial Mfg</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>FY2026 Q1</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>82.90000000000001</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>-0.028</v>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Net working capital days</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Industrial Mfg</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>FY2026 Q1</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="n">
+        <v>55</v>
+      </c>
+      <c r="E26" s="8" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="F26" s="8" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="G26" s="9" t="n">
+        <v>-0.008999999999999999</v>
+      </c>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Operating margin %</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Industrial Mfg</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>FY2026 Q1</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>-0.038</v>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>Amber</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>Cost-to-income %</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Industrial Mfg</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>FY2026 Q1</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="E28" s="8" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="F28" s="8" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="G28" s="9" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Revenue (MYR M)</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Property</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>FY2026 Q1</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>791.9</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>768.8</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>-23.1</v>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>-0.029</v>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>EBITDA (MYR M)</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Property</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>FY2026 Q1</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="n">
+        <v>128.3</v>
+      </c>
+      <c r="E30" s="8" t="n">
+        <v>139.6</v>
+      </c>
+      <c r="F30" s="8" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="G30" s="9" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Free cash flow (MYR M)</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Property</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>FY2026 Q1</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>-0.038</v>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>Amber</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>Net working capital days</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Property</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>FY2026 Q1</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="E32" s="8" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="F32" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G32" s="9" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>Amber</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Operating margin %</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Property</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>FY2026 Q1</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>-0.025</v>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>Cost-to-income %</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>Property</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>FY2026 Q1</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="n">
+        <v>39</v>
+      </c>
+      <c r="E34" s="8" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="F34" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G34" s="9" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Revenue (MYR M)</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Hospitality</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>FY2026 Q1</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>829.6</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>826.2</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="G35" s="6" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>EBITDA (MYR M)</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>Hospitality</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>FY2026 Q1</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="n">
+        <v>143</v>
+      </c>
+      <c r="E36" s="8" t="n">
+        <v>132.1</v>
+      </c>
+      <c r="F36" s="8" t="n">
+        <v>-10.9</v>
+      </c>
+      <c r="G36" s="9" t="n">
+        <v>-0.076</v>
+      </c>
+      <c r="H36" s="7" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Free cash flow (MYR M)</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Hospitality</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>FY2026 Q1</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>91.40000000000001</v>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="G37" s="6" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>Amber</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>Net working capital days</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>Hospitality</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>FY2026 Q1</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="n">
+        <v>57.8</v>
+      </c>
+      <c r="E38" s="8" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="F38" s="8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G38" s="9" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H38" s="7" t="inlineStr">
+        <is>
+          <t>Amber</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Operating margin %</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Hospitality</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>FY2026 Q1</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="G39" s="6" t="n">
+        <v>-0.026</v>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>Cost-to-income %</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>Hospitality</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>FY2026 Q1</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="E40" s="8" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="F40" s="8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G40" s="9" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="H40" s="7" t="inlineStr">
+        <is>
+          <t>Amber</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Revenue (MYR M)</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Digital Infra</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>FY2026 Q1</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>830.2</v>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>843.8</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="G41" s="6" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>EBITDA (MYR M)</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>Digital Infra</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>FY2026 Q1</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="n">
+        <v>134.3</v>
+      </c>
+      <c r="E42" s="8" t="n">
+        <v>145.6</v>
+      </c>
+      <c r="F42" s="8" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="G42" s="9" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="H42" s="7" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Free cash flow (MYR M)</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Digital Infra</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>FY2026 Q1</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>84.7</v>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>87.7</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G43" s="6" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>Amber</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>Net working capital days</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>Digital Infra</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>FY2026 Q1</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="E44" s="8" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="F44" s="8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G44" s="9" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="H44" s="7" t="inlineStr">
+        <is>
+          <t>Amber</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Operating margin %</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>Digital Infra</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>FY2026 Q1</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="E45" s="5" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G45" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>Cost-to-income %</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>Digital Infra</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>FY2026 Q1</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="E46" s="8" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="F46" s="8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G46" s="9" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="H46" s="7" t="inlineStr">
+        <is>
+          <t>Amber</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Revenue (MYR M)</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>Plantation</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>FY2026 Q1</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="n">
+        <v>804.3</v>
+      </c>
+      <c r="E47" s="5" t="n">
+        <v>815.6</v>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="G47" s="6" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>EBITDA (MYR M)</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>Plantation</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>FY2026 Q1</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="n">
+        <v>136.8</v>
+      </c>
+      <c r="E48" s="8" t="n">
+        <v>145.1</v>
+      </c>
+      <c r="F48" s="8" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="G48" s="9" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>Amber</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Free cash flow (MYR M)</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>Plantation</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>FY2026 Q1</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="n">
+        <v>87.2</v>
+      </c>
+      <c r="E49" s="5" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="F49" s="5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G49" s="6" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>Net working capital days</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>Plantation</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>FY2026 Q1</t>
+        </is>
+      </c>
+      <c r="D50" s="8" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="E50" s="8" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="F50" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G50" s="9" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="H50" s="7" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Operating margin %</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>Plantation</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>FY2026 Q1</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="E51" s="5" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="F51" s="5" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="G51" s="6" t="n">
+        <v>-0.013</v>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>Cost-to-income %</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>Plantation</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
+          <t>FY2026 Q1</t>
+        </is>
+      </c>
+      <c r="D52" s="8" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="E52" s="8" t="n">
+        <v>41</v>
+      </c>
+      <c r="F52" s="8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G52" s="9" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="H52" s="7" t="inlineStr">
+        <is>
+          <t>Amber</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
